--- a/excel/paper_progress_ripository_linked.xlsx
+++ b/excel/paper_progress_ripository_linked.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\학계 동향\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7247401-9395-44C7-9CB4-22B873EE6002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C971EF8F-5064-49AD-A3EA-9B9A913DE4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3015" yWindow="4620" windowWidth="21750" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4455" yWindow="9330" windowWidth="21750" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,6 +71,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -205,13 +208,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -226,9 +228,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -518,12 +520,12 @@
     <col min="4" max="4" width="9.625" customWidth="1"/>
     <col min="5" max="5" width="10.875" customWidth="1"/>
     <col min="6" max="6" width="14.125" customWidth="1"/>
-    <col min="7" max="7" width="11.625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="13" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -532,72 +534,72 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="11">
         <v>46303</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="9">
         <v>20</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="9">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="9">
         <v>1</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="10">
         <v>0</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="13">
         <f>E2/(D2+0.01)*F2*(1/(6-G2))</f>
         <v>8.3291687489588529E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+    <row r="3" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="11">
         <v>46303</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>0</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>0</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10">
         <v>0</v>
       </c>
-      <c r="G3" s="11">
-        <v>0</v>
-      </c>
-      <c r="H3" s="12">
+      <c r="H3" s="13">
         <f>E3/(D3+0.01)*F3*(1/(6-G3))</f>
         <v>0</v>
       </c>

--- a/excel/paper_progress_ripository_linked.xlsx
+++ b/excel/paper_progress_ripository_linked.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\학계 동향\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C971EF8F-5064-49AD-A3EA-9B9A913DE4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404D7A23-CDD5-4B6E-8DB5-D49A3688AC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="9330" windowWidth="21750" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5910" yWindow="810" windowWidth="21750" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -564,7 +564,7 @@
         <v>20</v>
       </c>
       <c r="E2" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="9">
         <v>1</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="H2" s="13">
         <f>E2/(D2+0.01)*F2*(1/(6-G2))</f>
-        <v>8.3291687489588529E-3</v>
+        <v>2.4987506246876557E-2</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
